--- a/data/trans_orig/P21-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>376100</t>
+          <t>377044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>411844</t>
+          <t>413960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334077</t>
+          <t>338485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>372454</t>
+          <t>371236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>724554</t>
+          <t>726057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>775347</t>
+          <t>773860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78340</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113164</t>
+          <t>113612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91892</t>
+          <t>93629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129280</t>
+          <t>126117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>179030</t>
+          <t>180142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230901</t>
+          <t>227935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601398</t>
+          <t>604136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>641351</t>
+          <t>642940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415696</t>
+          <t>416498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464684</t>
+          <t>462869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1032314</t>
+          <t>1033819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1093355</t>
+          <t>1095652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91777</t>
+          <t>91082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131204</t>
+          <t>129423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158873</t>
+          <t>160149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207065</t>
+          <t>207316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263732</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>323938</t>
+          <t>322598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>527468</t>
+          <t>528314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>565133</t>
+          <t>564158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>528957</t>
+          <t>533113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>573508</t>
+          <t>573525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1071482</t>
+          <t>1070192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1127421</t>
+          <t>1126660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71837</t>
+          <t>72704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109911</t>
+          <t>107974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108918</t>
+          <t>108709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152537</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190448</t>
+          <t>192200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246289</t>
+          <t>247070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>418619</t>
+          <t>420972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>454178</t>
+          <t>453550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>391803</t>
+          <t>393024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>428414</t>
+          <t>429517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>825166</t>
+          <t>826666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>874432</t>
+          <t>877864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>63155</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96609</t>
+          <t>95833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85616</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>122047</t>
+          <t>120666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>153676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>205290</t>
+          <t>203103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308144</t>
+          <t>308532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337780</t>
+          <t>337327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300887</t>
+          <t>301217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333851</t>
+          <t>331751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>617244</t>
+          <t>615988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662712</t>
+          <t>663424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76074</t>
+          <t>76269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67822</t>
+          <t>69279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99689</t>
+          <t>100036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122745</t>
+          <t>123631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166719</t>
+          <t>169700</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218476</t>
+          <t>216859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245633</t>
+          <t>243265</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>231795</t>
+          <t>230733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>264972</t>
+          <t>262135</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>459068</t>
+          <t>458466</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500237</t>
+          <t>498601</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>73637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>74363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104455</t>
+          <t>105558</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128723</t>
+          <t>129057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>168619</t>
+          <t>168539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140871</t>
+          <t>138996</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>165187</t>
+          <t>165790</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210558</t>
+          <t>210121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>245971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>360263</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>403717</t>
+          <t>403946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63755</t>
+          <t>64886</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>77260</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>111371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>121636</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>165257</t>
+          <t>165601</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>503666</t>
+          <t>496109</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>586503</t>
+          <t>585024</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>737331</t>
+          <t>742014</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>835566</t>
+          <t>839809</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1262273</t>
+          <t>1265979</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1389605</t>
+          <t>1392780</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>325374</t>
+          <t>324939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>361934</t>
+          <t>360380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281034</t>
+          <t>280481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>320457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>619789</t>
+          <t>617307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>670876</t>
+          <t>672986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89204</t>
+          <t>91048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>126547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109595</t>
+          <t>108578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148025</t>
+          <t>148323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209104</t>
+          <t>208387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262200</t>
+          <t>263747</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503068</t>
+          <t>500476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546629</t>
+          <t>546152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371196</t>
+          <t>368314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>418718</t>
+          <t>417969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887666</t>
+          <t>888123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949811</t>
+          <t>953809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135615</t>
+          <t>135558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179255</t>
+          <t>182302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188614</t>
+          <t>186758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234511</t>
+          <t>236186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338111</t>
+          <t>334861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>401100</t>
+          <t>399686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534849</t>
+          <t>532973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>575737</t>
+          <t>575672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>517862</t>
+          <t>513837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561988</t>
+          <t>561855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1062582</t>
+          <t>1060309</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128181</t>
+          <t>1124210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>99392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140610</t>
+          <t>141218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145696</t>
+          <t>146208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190688</t>
+          <t>195012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254308</t>
+          <t>259090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319946</t>
+          <t>322078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495883</t>
+          <t>495907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>532630</t>
+          <t>532797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>464074</t>
+          <t>462060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>507017</t>
+          <t>506242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>970485</t>
+          <t>971301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1028259</t>
+          <t>1029593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79650</t>
+          <t>79234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116700</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105016</t>
+          <t>106328</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147701</t>
+          <t>149520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>197895</t>
+          <t>195250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>252104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>336427</t>
+          <t>336229</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>368713</t>
+          <t>369087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>325337</t>
+          <t>324239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>359720</t>
+          <t>361279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>671962</t>
+          <t>674110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>720355</t>
+          <t>723607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56129</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>89157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81274</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116699</t>
+          <t>116211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>145291</t>
+          <t>143393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190383</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>237170</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>267497</t>
+          <t>265735</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>245899</t>
+          <t>242376</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>278616</t>
+          <t>277286</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>490848</t>
+          <t>492315</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>535466</t>
+          <t>536419</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67831</t>
+          <t>70162</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68132</t>
+          <t>70559</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100232</t>
+          <t>103035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>118819</t>
+          <t>115756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161807</t>
+          <t>159538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187538</t>
+          <t>188408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>225072</t>
+          <t>228391</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>264255</t>
+          <t>265590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>394676</t>
+          <t>391693</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>443175</t>
+          <t>441706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40191</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54030</t>
+          <t>53455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51968</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82076</t>
+          <t>80790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96666</t>
+          <t>96575</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>135856</t>
+          <t>132318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>155837</t>
+          <t>158944</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>203684</t>
+          <t>204825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>48047</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70044</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>71010</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>110159</t>
+          <t>108278</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>624815</t>
+          <t>625178</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>722862</t>
+          <t>719993</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>875423</t>
+          <t>876962</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986990</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1530467</t>
+          <t>1520447</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1673651</t>
+          <t>1673178</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309473</t>
+          <t>307213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>343705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284516</t>
+          <t>284016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317660</t>
+          <t>318509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601743</t>
+          <t>601104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>649642</t>
+          <t>648784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69709</t>
+          <t>69738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>103674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>73848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107880</t>
+          <t>108111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155290</t>
+          <t>156388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201522</t>
+          <t>200779</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470062</t>
+          <t>472654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508241</t>
+          <t>508921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401025</t>
+          <t>401716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442231</t>
+          <t>442586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882865</t>
+          <t>883291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938990</t>
+          <t>941850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76877</t>
+          <t>75848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116102</t>
+          <t>111420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118114</t>
+          <t>117153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159969</t>
+          <t>158678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205263</t>
+          <t>204146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257737</t>
+          <t>260377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>539116</t>
+          <t>536450</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>576882</t>
+          <t>576259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>497615</t>
+          <t>496871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539160</t>
+          <t>536480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1048837</t>
+          <t>1046941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1105902</t>
+          <t>1105194</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>84676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121226</t>
+          <t>122794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119606</t>
+          <t>121221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161973</t>
+          <t>161347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215985</t>
+          <t>214108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269750</t>
+          <t>270809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>533712</t>
+          <t>533716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>571149</t>
+          <t>570272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511334</t>
+          <t>511462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>551852</t>
+          <t>551877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1056334</t>
+          <t>1054036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1111806</t>
+          <t>1111159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29893</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>66916</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103018</t>
+          <t>103173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>85090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123460</t>
+          <t>123548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163162</t>
+          <t>163471</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215406</t>
+          <t>218817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>384414</t>
+          <t>386520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>417568</t>
+          <t>417277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>386823</t>
+          <t>385366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>422368</t>
+          <t>421900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>783533</t>
+          <t>780832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>832635</t>
+          <t>829990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>51661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82432</t>
+          <t>82599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65646</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100654</t>
+          <t>103255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125845</t>
+          <t>127044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172686</t>
+          <t>175236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>262244</t>
+          <t>261548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290222</t>
+          <t>289366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>279631</t>
+          <t>277411</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>312407</t>
+          <t>311172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>551346</t>
+          <t>550044</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>593521</t>
+          <t>593020</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>29273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>38161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64961</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84961</t>
+          <t>87675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98984</t>
+          <t>99771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139311</t>
+          <t>139593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199768</t>
+          <t>199454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221319</t>
+          <t>222461</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>279003</t>
+          <t>279568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>318716</t>
+          <t>318697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>489161</t>
+          <t>487797</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>534048</t>
+          <t>534728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43168</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57618</t>
+          <t>58451</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95232</t>
+          <t>94469</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>93563</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136562</t>
+          <t>134189</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>78036</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,47 +11854,47 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>106763</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>87875</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>132022</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>106763</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>87126</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>130455</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>474563</t>
+          <t>479418</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>559970</t>
+          <t>559088</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>652560</t>
+          <t>655834</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>747184</t>
+          <t>758355</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1152672</t>
+          <t>1156904</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1285740</t>
+          <t>1286180</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293396</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350987</t>
+          <t>351260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205982</t>
+          <t>208465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>248795</t>
+          <t>250707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>515386</t>
+          <t>514959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587606</t>
+          <t>587879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -12495,97 +12495,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1289</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6508</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>6339</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>110819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>101161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121836</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>194062</t>
+          <t>194843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311584</t>
+          <t>312733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354826</t>
+          <t>355294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360498</t>
+          <t>359881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436840</t>
+          <t>433674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689187</t>
+          <t>690626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780369</t>
+          <t>775371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,62 +12986,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5714</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68094</t>
+          <t>67675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111036</t>
+          <t>110754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74664</t>
+          <t>77830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151006</t>
+          <t>151623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153988</t>
+          <t>159059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244910</t>
+          <t>243388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>397754</t>
+          <t>398191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>436896</t>
+          <t>436744</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>392731</t>
+          <t>391751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>426559</t>
+          <t>424443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>801828</t>
+          <t>800066</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>855540</t>
+          <t>852929</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -13407,97 +13407,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1487</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99442</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138584</t>
+          <t>138147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114316</t>
+          <t>116432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>149124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221673</t>
+          <t>224284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>275385</t>
+          <t>277147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>658565</t>
+          <t>657097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>819663</t>
+          <t>821973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>531651</t>
+          <t>530502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>577209</t>
+          <t>574698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1207731</t>
+          <t>1208886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1416182</t>
+          <t>1415467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64390</t>
+          <t>61290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>216805</t>
+          <t>221577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>132817</t>
+          <t>134037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>179031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174721</t>
+          <t>179203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>379102</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>428511</t>
+          <t>428561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>463441</t>
+          <t>463319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>399134</t>
+          <t>400058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>428552</t>
+          <t>429802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>837362</t>
+          <t>836014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>882184</t>
+          <t>883936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>93745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>129199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112567</t>
+          <t>112146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142101</t>
+          <t>140892</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216513</t>
+          <t>215419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261178</t>
+          <t>262171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>292024</t>
+          <t>291962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316110</t>
+          <t>315887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131519</t>
+          <t>151155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>475537</t>
+          <t>475566</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>337756</t>
+          <t>331864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>786158</t>
+          <t>785236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71221</t>
+          <t>72494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127464</t>
+          <t>127624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>474811</t>
+          <t>454536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181014</t>
+          <t>181837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>634200</t>
+          <t>640818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213108</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>234220</t>
+          <t>235166</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>288658</t>
+          <t>289414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316222</t>
+          <t>315039</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>508197</t>
+          <t>510038</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>543540</t>
+          <t>544460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43677</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64224</t>
+          <t>63504</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>94494</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118706</t>
+          <t>118952</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>143914</t>
+          <t>143515</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>178515</t>
+          <t>176297</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>512316</t>
+          <t>509372</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>729500</t>
+          <t>735800</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>843702</t>
+          <t>843271</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1555264</t>
+          <t>1507931</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1459473</t>
+          <t>1479337</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2251053</t>
+          <t>2298887</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>377044</t>
+          <t>376828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>413960</t>
+          <t>413445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>338485</t>
+          <t>337434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371236</t>
+          <t>372272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>726057</t>
+          <t>724146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>773860</t>
+          <t>775000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77354</t>
+          <t>77370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113612</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>92225</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126117</t>
+          <t>126541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>180142</t>
+          <t>179045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>229902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>604136</t>
+          <t>603436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642940</t>
+          <t>642358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416498</t>
+          <t>415693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462869</t>
+          <t>463768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1033819</t>
+          <t>1030190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1095652</t>
+          <t>1093046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91082</t>
+          <t>90479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129423</t>
+          <t>129383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160149</t>
+          <t>160091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207316</t>
+          <t>207483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260088</t>
+          <t>263261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322598</t>
+          <t>326589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>528314</t>
+          <t>529346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>564158</t>
+          <t>566271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533113</t>
+          <t>530812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>573525</t>
+          <t>572971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1070192</t>
+          <t>1071689</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1126660</t>
+          <t>1126962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72704</t>
+          <t>70629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>107448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108709</t>
+          <t>109163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147991</t>
+          <t>150876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192200</t>
+          <t>190712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247070</t>
+          <t>246042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>420972</t>
+          <t>418709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>453550</t>
+          <t>454175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>393024</t>
+          <t>393383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>429517</t>
+          <t>428262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826666</t>
+          <t>826165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>877864</t>
+          <t>874731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63155</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95833</t>
+          <t>95749</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>85549</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>119900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>153676</t>
+          <t>155754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>203103</t>
+          <t>203766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308532</t>
+          <t>308594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337327</t>
+          <t>336710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301217</t>
+          <t>300007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331751</t>
+          <t>333780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615988</t>
+          <t>617606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>663424</t>
+          <t>661349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>48249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76269</t>
+          <t>76581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100036</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123631</t>
+          <t>124531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169700</t>
+          <t>166914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>216859</t>
+          <t>216637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243265</t>
+          <t>244115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>230733</t>
+          <t>231301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>262135</t>
+          <t>264717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>458466</t>
+          <t>460166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>498601</t>
+          <t>503410</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73637</t>
+          <t>73933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74363</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105558</t>
+          <t>104223</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>129057</t>
+          <t>125421</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>168539</t>
+          <t>167277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>165790</t>
+          <t>165000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210121</t>
+          <t>211254</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245971</t>
+          <t>246314</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>360263</t>
+          <t>360954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>403946</t>
+          <t>403534</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>39013</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64886</t>
+          <t>62345</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76967</t>
+          <t>77397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111371</t>
+          <t>110123</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>122334</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>165601</t>
+          <t>166379</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>49881</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>71617</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>496109</t>
+          <t>500866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>585024</t>
+          <t>584583</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>742014</t>
+          <t>735146</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>839809</t>
+          <t>833843</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1265979</t>
+          <t>1262898</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1392780</t>
+          <t>1398898</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324939</t>
+          <t>324153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>360380</t>
+          <t>361335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280481</t>
+          <t>281031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>320457</t>
+          <t>319073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617307</t>
+          <t>618437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>672986</t>
+          <t>670648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>90712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126547</t>
+          <t>127031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108578</t>
+          <t>110157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148323</t>
+          <t>148436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>208387</t>
+          <t>210217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>262260</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500476</t>
+          <t>500123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546152</t>
+          <t>546991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368314</t>
+          <t>372179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417969</t>
+          <t>420681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888123</t>
+          <t>889215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953809</t>
+          <t>958081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135558</t>
+          <t>136659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182302</t>
+          <t>182202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186758</t>
+          <t>184748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>236186</t>
+          <t>234084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,47 +5348,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>38,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>366912</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>330345</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>397362</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>30,65%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>366912</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>334861</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>399686</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>532973</t>
+          <t>532251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>575672</t>
+          <t>575369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513837</t>
+          <t>514669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561855</t>
+          <t>561988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1060309</t>
+          <t>1060655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1124210</t>
+          <t>1128710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99392</t>
+          <t>100599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>142115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146208</t>
+          <t>146080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195012</t>
+          <t>193725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259090</t>
+          <t>253117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322078</t>
+          <t>319991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495907</t>
+          <t>495452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>532797</t>
+          <t>532119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>462060</t>
+          <t>463281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>506242</t>
+          <t>507819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>971301</t>
+          <t>968889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1029593</t>
+          <t>1028735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,47 +6147,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>11875</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>11514</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79234</t>
+          <t>80452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>117522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106328</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>149296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>195250</t>
+          <t>195992</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252104</t>
+          <t>255632</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>336229</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>369087</t>
+          <t>369462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324239</t>
+          <t>325427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361279</t>
+          <t>362328</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>674110</t>
+          <t>674663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>723607</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89157</t>
+          <t>85653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79824</t>
+          <t>79147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116211</t>
+          <t>114448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143393</t>
+          <t>145079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189893</t>
+          <t>189554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235121</t>
+          <t>237844</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>265735</t>
+          <t>265783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>242376</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277286</t>
+          <t>278282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>492315</t>
+          <t>489524</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>536419</t>
+          <t>534233</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>39950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70559</t>
+          <t>68859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103035</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115756</t>
+          <t>119387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159538</t>
+          <t>161246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157602</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>188424</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228391</t>
+          <t>227170</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>265590</t>
+          <t>265713</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>391693</t>
+          <t>392882</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>441706</t>
+          <t>444483</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80790</t>
+          <t>81788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96575</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132318</t>
+          <t>133462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>158944</t>
+          <t>156218</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>204825</t>
+          <t>205662</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2665805</t>
+          <t>2670441</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2763114</t>
+          <t>2770323</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2512312</t>
+          <t>2514979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2626234</t>
+          <t>2623825</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5214702</t>
+          <t>5214272</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5365185</t>
+          <t>5361408</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>48711</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>40074</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>72051</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>108119</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>625178</t>
+          <t>623013</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>719993</t>
+          <t>718609</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>876962</t>
+          <t>878723</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>986990</t>
+          <t>988899</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1520447</t>
+          <t>1529796</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1673178</t>
+          <t>1673569</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>307213</t>
+          <t>307423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343705</t>
+          <t>344427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>284016</t>
+          <t>282354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318509</t>
+          <t>317169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601104</t>
+          <t>603272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>648784</t>
+          <t>651911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69738</t>
+          <t>68587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103674</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73848</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108111</t>
+          <t>108315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>156388</t>
+          <t>153176</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200779</t>
+          <t>200654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472654</t>
+          <t>470469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508921</t>
+          <t>507270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401716</t>
+          <t>400852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442586</t>
+          <t>441426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>883291</t>
+          <t>884875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941850</t>
+          <t>940346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>885</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75848</t>
+          <t>76438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111420</t>
+          <t>113704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117153</t>
+          <t>118572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158678</t>
+          <t>158456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204146</t>
+          <t>204631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260377</t>
+          <t>259880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536450</t>
+          <t>538340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>576259</t>
+          <t>577056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>496871</t>
+          <t>497362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>536480</t>
+          <t>538697</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1046941</t>
+          <t>1046712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1105194</t>
+          <t>1104789</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84676</t>
+          <t>83431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122794</t>
+          <t>121289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121221</t>
+          <t>120836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161347</t>
+          <t>161322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214108</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270809</t>
+          <t>271618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>533716</t>
+          <t>533201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>570272</t>
+          <t>570866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511462</t>
+          <t>511378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>551877</t>
+          <t>550871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1054036</t>
+          <t>1054550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1111159</t>
+          <t>1110314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,47 +10030,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>19862</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>12515</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>31651</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>19862</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>11484</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>29802</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66916</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103173</t>
+          <t>101814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85090</t>
+          <t>85609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123548</t>
+          <t>124648</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163471</t>
+          <t>164416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>218817</t>
+          <t>216426</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>386520</t>
+          <t>385683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>417277</t>
+          <t>418641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>385366</t>
+          <t>385475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>421900</t>
+          <t>422110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>780832</t>
+          <t>781580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>829990</t>
+          <t>831593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>50823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82599</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>66349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103255</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127044</t>
+          <t>125498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175236</t>
+          <t>174975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>261548</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>289366</t>
+          <t>289586</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277411</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>311172</t>
+          <t>310729</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>550044</t>
+          <t>550295</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>593020</t>
+          <t>593266</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64198</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55658</t>
+          <t>55499</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>86428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99771</t>
+          <t>99043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139593</t>
+          <t>141177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199454</t>
+          <t>198619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222461</t>
+          <t>221858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>279568</t>
+          <t>282201</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>318697</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>487797</t>
+          <t>488871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>534728</t>
+          <t>534543</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36086</t>
+          <t>34401</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49649</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58451</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94469</t>
+          <t>93761</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93563</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>135756</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2778181</t>
+          <t>2772776</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2862451</t>
+          <t>2858318</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2720750</t>
+          <t>2724242</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2823808</t>
+          <t>2824294</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5529828</t>
+          <t>5522158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5664986</t>
+          <t>5657200</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>44524</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>78948</t>
+          <t>78712</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>87875</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>132022</t>
+          <t>131209</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>479418</t>
+          <t>480312</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>559088</t>
+          <t>563714</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>655834</t>
+          <t>657122</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>758355</t>
+          <t>754292</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1156904</t>
+          <t>1160472</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1286180</t>
+          <t>1287024</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>334136</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>300732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351260</t>
+          <t>355550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>229583</t>
+          <t>265249</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208465</t>
+          <t>241171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250707</t>
+          <t>287425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>553692</t>
+          <t>599386</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>514959</t>
+          <t>564562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587879</t>
+          <t>631081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -12535,12 +12535,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -12570,12 +12570,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>52243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80100</t>
+          <t>93786</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>71349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101161</t>
+          <t>117447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155978</t>
+          <t>167442</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121875</t>
+          <t>135236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>194843</t>
+          <t>202088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>335277</t>
+          <t>379425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312733</t>
+          <t>354659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355294</t>
+          <t>402056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>388743</t>
+          <t>370563</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359881</t>
+          <t>350256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433674</t>
+          <t>392817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>724020</t>
+          <t>749987</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690626</t>
+          <t>712360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775371</t>
+          <t>777046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87141</t>
+          <t>96263</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67675</t>
+          <t>73674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110754</t>
+          <t>121476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>130520</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77830</t>
+          <t>108266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151623</t>
+          <t>150827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>209902</t>
+          <t>226784</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159059</t>
+          <t>199867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243388</t>
+          <t>265035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>418994</t>
+          <t>492224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>398191</t>
+          <t>469288</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>436744</t>
+          <t>511019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>410327</t>
+          <t>469551</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>391751</t>
+          <t>450341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>424443</t>
+          <t>486451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>829322</t>
+          <t>961775</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>800066</t>
+          <t>931876</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>852929</t>
+          <t>988996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>117344</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138147</t>
+          <t>151549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>130548</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116432</t>
+          <t>134067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149124</t>
+          <t>170177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>247891</t>
+          <t>279580</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224284</t>
+          <t>252359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277147</t>
+          <t>309479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>727858</t>
+          <t>525361</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>657097</t>
+          <t>500227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821973</t>
+          <t>546321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>550182</t>
+          <t>559521</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>530502</t>
+          <t>540357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574698</t>
+          <t>576616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1278040</t>
+          <t>1084882</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1208886</t>
+          <t>1052055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1415467</t>
+          <t>1113829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152084</t>
+          <t>167107</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61290</t>
+          <t>147522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>221577</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159277</t>
+          <t>173311</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134037</t>
+          <t>156197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179031</t>
+          <t>192331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>311361</t>
+          <t>340417</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179203</t>
+          <t>311015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380528</t>
+          <t>372482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>445961</t>
+          <t>484391</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>428561</t>
+          <t>463127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>463319</t>
+          <t>501284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>414667</t>
+          <t>461354</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>400058</t>
+          <t>444557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>429802</t>
+          <t>477214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>860627</t>
+          <t>945745</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>836014</t>
+          <t>920546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883936</t>
+          <t>970423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>111615</t>
+          <t>120634</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93745</t>
+          <t>103597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,17 +14462,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>126494</t>
+          <t>141050</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112146</t>
+          <t>125865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140892</t>
+          <t>157837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>238109</t>
+          <t>261685</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215419</t>
+          <t>237424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262171</t>
+          <t>286431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>335196</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>291962</t>
+          <t>320831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315887</t>
+          <t>346019</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>311257</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151155</t>
+          <t>323198</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>475566</t>
+          <t>349015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>615380</t>
+          <t>671548</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>331864</t>
+          <t>652613</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>785236</t>
+          <t>689607</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -14770,22 +14770,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>60685</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>57563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72494</t>
+          <t>82734</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>293133</t>
+          <t>97851</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127624</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>454536</t>
+          <t>110387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>353817</t>
+          <t>166058</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181837</t>
+          <t>148370</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>640818</t>
+          <t>184540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>224818</t>
+          <t>246876</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>214284</t>
+          <t>233316</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235166</t>
+          <t>257177</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>302445</t>
+          <t>330847</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>289414</t>
+          <t>315403</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>315039</t>
+          <t>344519</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>527263</t>
+          <t>577723</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>510038</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>544460</t>
+          <t>597286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>31625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52710</t>
+          <t>57971</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42970</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>106304</t>
+          <t>115049</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>94494</t>
+          <t>101315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118952</t>
+          <t>128155</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>173020</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>143515</t>
+          <t>155194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>176297</t>
+          <t>190472</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2781140</t>
+          <t>2797610</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2702110</t>
+          <t>2744189</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2933540</t>
+          <t>2850242</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2607205</t>
+          <t>2793437</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2118192</t>
+          <t>2749218</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2779790</t>
+          <t>2839288</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5388344</t>
+          <t>5591047</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4788190</t>
+          <t>5515804</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5585163</t>
+          <t>5660354</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -15682,67 +15682,67 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>32194</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>24033</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>42959</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>27870</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>19935</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>37392</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>65876</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>657457</t>
+          <t>712452</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>509372</t>
+          <t>658173</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>735800</t>
+          <t>765278</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1018616</t>
+          <t>902535</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>843271</t>
+          <t>856225</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1507931</t>
+          <t>945619</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1676074</t>
+          <t>1614987</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1479337</t>
+          <t>1545399</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2298887</t>
+          <t>1687288</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
